--- a/data/incremental/incremental_03_lo_barnechea_manual.xlsx
+++ b/data/incremental/incremental_03_lo_barnechea_manual.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Restaurantes" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Restaurantes'!$A$1:$AG$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Restaurantes'!$A$1:$AG$31</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG28"/>
+  <dimension ref="A1:AG31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -460,7 +460,7 @@
     <col width="15" customWidth="1" min="30" max="30"/>
     <col width="12" customWidth="1" min="31" max="31"/>
     <col width="17" customWidth="1" min="32" max="32"/>
-    <col width="42" customWidth="1" min="33" max="33"/>
+    <col width="22" customWidth="1" min="33" max="33"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -703,7 +703,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>394</t>
+          <t>398</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Barrica+94/@-33.3567819,-70.5400355,17z/data=!3m1!4b1!4m6!3m5!1s0x9662c59ac22dc56b:0x1403cd9464826478!8m2!3d-33.3567819!4d-70.5400355!16s%2Fg%2F11bwh9wr9_?authuser=0&amp;hl=es-419&amp;entry=ttu&amp;g_ep=EgoyMDI2MDUyMC4wIKXMDSoASAFQAw%3D%3D</t>
+          <t>https://www.google.com/maps/place/Barrica+94/data=!4m7!3m6!1s0x9662c59ac22dc56b:0x1403cd9464826478!8m2!3d-33.3567819!4d-70.5400355!16s%2Fg%2F11bwh9wr9_!19sChIJa8UtwprFYpYReGSCZJTNAxQ?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1148,52 +1148,52 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Delfina Bistro</t>
+          <t>Aleman Experto La Dehesa</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.4</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>06</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Av. La Dehesa 1201, 7690277 Lo Barnechea, Región Metropolitana</t>
+          <t>Av. La Dehesa 1670, 7690253 Lo Barnechea, Región Metropolitana</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>9 7807 1773</t>
+          <t>(2) 3267 1637</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/delfina_bistro</t>
+          <t>http://www.alemanexperto.cl/</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Taberna</t>
+          <t>Restaurante</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Delfina+Bistro/data=!4m7!3m6!1s0x9662cb0044df1c5d:0xcb72375c0611c704!8m2!3d-33.36034!4d-70.5148406!16s%2Fg%2F11xp4kcj0w!19sChIJXRzfRADLYpYRBMcRBlw3css?authuser=0&amp;hl=es-419&amp;rclk=1</t>
+          <t>https://www.google.com/maps/place/Aleman+Experto+La+Dehesa/data=!4m7!3m6!1s0x9662cbdd07f40b67:0x915b5dbe49b78295!8m2!3d-33.3573537!4d-70.5176429!16s%2Fg%2F11g8ygtnln!19sChIJZwv0B93LYpYRlYK3Sb5dW5E?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-33.36034</t>
+          <t>-33.3573537</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-70.5148406</t>
+          <t>-70.5176429</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1251,52 +1251,52 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Doña Tina</t>
+          <t>Delfina Bistro</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>4.8</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>103</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Cam. los Refugios del Arrayan 15125, Lo Barnechea, Región Metropolitana</t>
+          <t>Av. La Dehesa 1201, 7690277 Lo Barnechea, Región Metropolitana</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>(2) 2321 6546</t>
+          <t>9 7807 1773</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>http://www.donatina.cl/</t>
+          <t>https://www.instagram.com/delfina_bistro</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Restaurante</t>
+          <t>Taberna</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Do%C3%B1a+Tina/@-33.3610734,-70.4920546,17z/data=!3m1!4b1!4m6!3m5!1s0x9662cb90b5ce7e15:0xd77184d3077867ff!8m2!3d-33.3610734!4d-70.4920546!16s%2Fg%2F1hjgq14dc?authuser=0&amp;hl=es-419&amp;entry=ttu&amp;g_ep=EgoyMDI2MDUyMC4wIKXMDSoASAFQAw%3D%3D</t>
+          <t>https://www.google.com/maps/place/Delfina+Bistro/data=!4m7!3m6!1s0x9662cb0044df1c5d:0xcb72375c0611c704!8m2!3d-33.36034!4d-70.5148406!16s%2Fg%2F11xp4kcj0w!19sChIJXRzfRADLYpYRBMcRBlw3css?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-33.3610734</t>
+          <t>-33.36034</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-70.4920546</t>
+          <t>-70.5148406</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1457,7 +1457,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Aleman Experto La Dehesa</t>
+          <t>Doña Tina</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1472,17 +1472,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Av. La Dehesa 1670, 7690253 Lo Barnechea, Región Metropolitana</t>
+          <t>Cam. los Refugios del Arrayan 15125, Lo Barnechea, Región Metropolitana</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>(2) 3267 1637</t>
+          <t>(2) 2321 6546</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>http://www.alemanexperto.cl/</t>
+          <t>http://www.donatina.cl/</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1492,17 +1492,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Aleman+Experto+La+Dehesa/data=!4m7!3m6!1s0x9662cbdd07f40b67:0x915b5dbe49b78295!8m2!3d-33.3573537!4d-70.5176429!16s%2Fg%2F11g8ygtnln!19sChIJZwv0B93LYpYRlYK3Sb5dW5E?authuser=0&amp;hl=es-419&amp;rclk=1</t>
+          <t>https://www.google.com/maps/place/Do%C3%B1a+Tina/data=!4m7!3m6!1s0x9662cb90b5ce7e15:0xd77184d3077867ff!8m2!3d-33.3610734!4d-70.4920546!16s%2Fg%2F1hjgq14dc!19sChIJFX7OtZDLYpYR_2d4B9OEcdc?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-33.3573537</t>
+          <t>-33.3610734</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-70.5176429</t>
+          <t>-70.4920546</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1527,7 +1527,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1663,52 +1663,52 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Rishtedar La Dehesa</t>
+          <t>Alemán Experto Los Trapenses</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>100</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>El Rodeo 12850, Local 74 y 75, Lo Barnechea, Región Metropolitana</t>
+          <t>Cam. Los Trapenses 3515, Lo Barnechea, Región Metropolitana</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>(2) 3345 4142</t>
+          <t>9 9845 0513</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://rishtedar.cl/</t>
+          <t>http://www.alemanexperto.cl/</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Restaurante indio</t>
+          <t>Restaurante</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Rishtedar+La+Dehesa/data=!4m7!3m6!1s0x9662cbe6c5693217:0x1785539e3974932c!8m2!3d-33.3524375!4d-70.5196951!16s%2Fg%2F11xtxwszz2!19sChIJFzJpxebLYpYRLJN0OZ5ThRc?authuser=0&amp;hl=es-419&amp;rclk=1</t>
+          <t>https://www.google.com/maps/place/Alem%C3%A1n+Experto+Los+Trapenses/data=!4m7!3m6!1s0x9662c90076f353a1:0x56ca1ab25f5a3687!8m2!3d-33.343684!4d-70.5445141!16s%2Fg%2F11x73w3tj6!19sChIJoVPzdgDJYpYRhzZaX7IaylY?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-33.3524375</t>
+          <t>-33.343684</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-70.5196951</t>
+          <t>-70.5445141</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1733,7 +1733,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1766,48 +1766,52 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Fiamma</t>
+          <t>Hocha Restaurante de Comida Típica Taiwanesa - Patio La Dehesa</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>343</t>
+          <t>85</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Av. La Dehesa 1445, local 6224, 7690130 Lo Barnechea, Región Metropolitana</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr"/>
+          <t>Av. José Alcalde Délano 10425, Local 21, 7690324 Lo Barnechea, Región Metropolitana</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>(2) 2954 7934</t>
+        </is>
+      </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://fiammaristorante.cl/</t>
+          <t>http://www.hocha.cl/</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Restaurante italiano</t>
+          <t>Restaurante asiático</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Fiamma/data=!4m7!3m6!1s0x9662cb0026674221:0xadb31afc1247a4da!8m2!3d-33.3585606!4d-70.5158902!16s%2Fg%2F11yczhp7tn!19sChIJIUJnJgDLYpYR2qRHEvwas60?authuser=0&amp;hl=es-419&amp;rclk=1</t>
+          <t>https://www.google.com/maps/place/Hocha+Restaurante+de+Comida+T%C3%ADpica+Taiwanesa+-+Patio+La+Dehesa/data=!4m7!3m6!1s0x9662c97611858c27:0x9c7c6196c38ccd8!8m2!3d-33.3594746!4d-70.5433854!16s%2Fg%2F11sd_8p15m!19sChIJJ4yFEXbJYpYR2Mw4bBnGxwk?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-33.3585606</t>
+          <t>-33.3594746</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-70.5158902</t>
+          <t>-70.5433854</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1832,12 +1836,12 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Sin teléfono</t>
+          <t>Completo</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
@@ -1860,61 +1864,57 @@
       <c r="AD13" t="inlineStr"/>
       <c r="AE13" t="inlineStr"/>
       <c r="AF13" t="inlineStr"/>
-      <c r="AG13" t="inlineStr">
-        <is>
-          <t>Sin teléfono visible</t>
-        </is>
-      </c>
+      <c r="AG13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Bambinolli Restaurante</t>
+          <t>Rishtedar La Dehesa</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>52</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>El Rodeo 13350, 5006070 Lo Barnechea, Región Metropolitana</t>
+          <t>El Rodeo 12850, Local 74 y 75, Lo Barnechea, Región Metropolitana</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>9 3239 2425</t>
+          <t>(2) 3345 4142</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/bambinollirestaurante/</t>
+          <t>https://rishtedar.cl/</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Restaurante</t>
+          <t>Restaurante indio</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Bambinolli+Restaurante/@-33.3514323,-70.5120598,17z/data=!3m1!4b1!4m6!3m5!1s0x9662cbaf9cb86af5:0x4288af43e3d517c5!8m2!3d-33.3514323!4d-70.5120598!16s%2Fg%2F11xw87swbc?authuser=0&amp;hl=es-419&amp;entry=ttu&amp;g_ep=EgoyMDI2MDUyMC4wIKXMDSoASAFQAw%3D%3D</t>
+          <t>https://www.google.com/maps/place/Rishtedar+La+Dehesa/data=!4m7!3m6!1s0x9662cbe6c5693217:0x1785539e3974932c!8m2!3d-33.3524375!4d-70.5196951!16s%2Fg%2F11xtxwszz2!19sChIJFzJpxebLYpYRLJN0OZ5ThRc?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-33.3514323</t>
+          <t>-33.3524375</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-70.5120598</t>
+          <t>-70.5196951</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1939,7 +1939,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1972,32 +1972,32 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Nelí Portal La Dehesa</t>
+          <t>Kiara Nikkei</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>386</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Av. La Dehesa 1445, local 1108, 7690130 Lo Barnechea, Región Metropolitana</t>
+          <t>El Rodeo 13332, 7690908 Lo Barnechea, Región Metropolitana</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>9 7949 2016</t>
+          <t>(2) 3210 4200</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://www.neli.cl/</t>
+          <t>https://kiaranikkei.cl/</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2007,17 +2007,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Nel%C3%AD+Portal+La+Dehesa/data=!4m7!3m6!1s0x9662cb76dd6c75a1:0xef4c811b5d84772f!8m2!3d-33.3573513!4d-70.5151516!16s%2Fg%2F11ww0wwdnp!19sChIJoXVs3XbLYpYRL3eEXRuBTO8?authuser=0&amp;hl=es-419&amp;rclk=1</t>
+          <t>https://www.google.com/maps/place/Kiara+Nikkei/data=!4m7!3m6!1s0x9662cb8b33dbf8af:0x7de2d4768a1e5777!8m2!3d-33.3513773!4d-70.5124452!16s%2Fg%2F11s4tggl8_!19sChIJr_jbM4vLYpYRd1ceinbU4n0?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-33.3573513</t>
+          <t>-33.3513773</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-70.5151516</t>
+          <t>-70.5124452</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -2042,7 +2042,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2075,17 +2075,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>El Japonés - Portal La Dehesa</t>
+          <t>Fiamma</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>731</t>
+          <t>343</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2096,27 +2096,27 @@
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://eljaponeschile.com/</t>
+          <t>https://fiammaristorante.cl/</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Restaurante japonés</t>
+          <t>Restaurante italiano</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/El+Japon%C3%A9s+-+Portal+La+Dehesa/data=!4m7!3m6!1s0x9662cb005123129b:0x55f574911866195d!8m2!3d-33.3587407!4d-70.5158683!16s%2Fg%2F11x0mhfd8d!19sChIJmxIjUQDLYpYRXRlmGJF09VU?authuser=0&amp;hl=es-419&amp;rclk=1</t>
+          <t>https://www.google.com/maps/place/Fiamma/data=!4m7!3m6!1s0x9662cb0026674221:0xadb31afc1247a4da!8m2!3d-33.3585606!4d-70.5158902!16s%2Fg%2F11yczhp7tn!19sChIJIUJnJgDLYpYR2qRHEvwas60?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-33.3587407</t>
+          <t>-33.3585606</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-70.5158683</t>
+          <t>-70.5158902</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2178,52 +2178,48 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sabor y Aroma</t>
+          <t>Tommy Beans La Dehesa</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>44</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Av. Raúl Labbé 12559, 7690554 Lo Barnechea, Región Metropolitana</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>(2) 3264 3715</t>
-        </is>
-      </c>
+          <t>Av. La Dehesa 2035, local 5, 7691188 Lo Barnechea, Región Metropolitana</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://saboryaroma.cl/</t>
+          <t>http://www.tommybeans.cl/</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Restaurante peruano</t>
+          <t>Restaurante mexicano</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Sabor+y+Aroma/data=!4m7!3m6!1s0x9662cbe5e86c4a7f:0xd5d5180f7b0dcda7!8m2!3d-33.3653921!4d-70.5156354!16s%2Fg%2F11c22w2c91!19sChIJf0ps6OXLYpYRp80New8Y1dU?authuser=0&amp;hl=es-419&amp;rclk=1</t>
+          <t>https://www.google.com/maps/place/Tommy+Beans+La+Dehesa/data=!4m7!3m6!1s0x9662cb005dca5703:0x414e11a4df2d0974!8m2!3d-33.3520201!4d-70.5184035!16s%2Fg%2F11y0pm7506!19sChIJA1fKXQDLYpYRdAkt36QRTkE?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-33.3653921</t>
+          <t>-33.3520201</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-70.5156354</t>
+          <t>-70.5184035</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -2248,12 +2244,12 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Completo</t>
+          <t>Sin teléfono</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
@@ -2276,12 +2272,16 @@
       <c r="AD17" t="inlineStr"/>
       <c r="AE17" t="inlineStr"/>
       <c r="AF17" t="inlineStr"/>
-      <c r="AG17" t="inlineStr"/>
+      <c r="AG17" t="inlineStr">
+        <is>
+          <t>Sin teléfono visible</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Mitsuha Nikkei</t>
+          <t>El Japonés - Portal La Dehesa</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2291,42 +2291,38 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>733</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Padre Alfredo Arteaga Barros 1929, 7690083 Santiago, Lo Barnechea, Región Metropolitana</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>9 7947 2619</t>
-        </is>
-      </c>
+          <t>Av. La Dehesa 1445, local 6224, 7690130 Lo Barnechea, Región Metropolitana</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://www.mitsuhanikkei.cl/</t>
+          <t>https://eljaponeschile.com/</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Restaurante de sushi</t>
+          <t>Restaurante japonés</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Mitsuha+Nikkei/data=!4m7!3m6!1s0x9662cbb752bf2579:0x9a980ca317548339!8m2!3d-33.3524553!4d-70.5103536!16s%2Fg%2F11y2mw3138!19sChIJeSW_UrfLYpYROYNUF6MMmJo?authuser=0&amp;hl=es-419&amp;rclk=1</t>
+          <t>https://www.google.com/maps/place/El+Japon%C3%A9s+-+Portal+La+Dehesa/data=!4m7!3m6!1s0x9662cb005123129b:0x55f574911866195d!8m2!3d-33.3587407!4d-70.5158683!16s%2Fg%2F11x0mhfd8d!19sChIJmxIjUQDLYpYRXRlmGJF09VU?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-33.3524553</t>
+          <t>-33.3587407</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-70.5103536</t>
+          <t>-70.5158683</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -2351,12 +2347,12 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Completo</t>
+          <t>Sin teléfono</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
@@ -2379,37 +2375,41 @@
       <c r="AD18" t="inlineStr"/>
       <c r="AE18" t="inlineStr"/>
       <c r="AF18" t="inlineStr"/>
-      <c r="AG18" t="inlineStr"/>
+      <c r="AG18" t="inlineStr">
+        <is>
+          <t>Sin teléfono visible</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Kiara Nikkei</t>
+          <t>Nelí Portal La Dehesa</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>4.4</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>103</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>El Rodeo 13332, 7690908 Lo Barnechea, Región Metropolitana</t>
+          <t>Av. La Dehesa 1445, local 1108, 7690130 Lo Barnechea, Región Metropolitana</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>(2) 3210 4200</t>
+          <t>9 7949 2016</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://kiaranikkei.cl/</t>
+          <t>https://www.neli.cl/</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2419,17 +2419,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Kiara+Nikkei/data=!4m7!3m6!1s0x9662cb8b33dbf8af:0x7de2d4768a1e5777!8m2!3d-33.3513773!4d-70.5124452!16s%2Fg%2F11s4tggl8_!19sChIJr_jbM4vLYpYRd1ceinbU4n0?authuser=0&amp;hl=es-419&amp;rclk=1</t>
+          <t>https://www.google.com/maps/place/Nel%C3%AD+Portal+La+Dehesa/data=!4m7!3m6!1s0x9662cb76dd6c75a1:0xef4c811b5d84772f!8m2!3d-33.3573513!4d-70.5151516!16s%2Fg%2F11ww0wwdnp!19sChIJoXVs3XbLYpYRL3eEXRuBTO8?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-33.3513773</t>
+          <t>-33.3573513</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-70.5124452</t>
+          <t>-70.5151516</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2487,32 +2487,32 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ZÍA Bistró &amp; Café</t>
+          <t>Bambinolli Restaurante</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>142</t>
+          <t>633</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>El Rodeo 13453, 7690098 Lo Barnechea, Región Metropolitana</t>
+          <t>El Rodeo 13350, 5006070 Lo Barnechea, Región Metropolitana</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>9 3647 8658</t>
+          <t>9 3239 2425</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>http://www.ziabistro.cl/</t>
+          <t>https://www.instagram.com/bambinollirestaurante/</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -2522,17 +2522,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Z%C3%8DA+Bistr%C3%B3+%26+Caf%C3%A9/@-33.3519791,-70.5121117,17z/data=!3m1!4b1!4m6!3m5!1s0x9662cb0bb59653bf:0x621cf567cf02bc40!8m2!3d-33.3519791!4d-70.5121117!16s%2Fg%2F11lv74fdpq?authuser=0&amp;hl=es-419&amp;entry=ttu&amp;g_ep=EgoyMDI2MDUyMC4wIKXMDSoASAFQAw%3D%3D</t>
+          <t>https://www.google.com/maps/place/Bambinolli+Restaurante/data=!4m7!3m6!1s0x9662cbaf9cb86af5:0x4288af43e3d517c5!8m2!3d-33.3514323!4d-70.5120598!16s%2Fg%2F11xw87swbc!19sChIJ9Wq4nK_LYpYRxRfV40OviEI?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-33.3519791</t>
+          <t>-33.3514323</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-70.5121117</t>
+          <t>-70.5120598</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -2557,7 +2557,7 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2567,7 +2567,7 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="R20" t="inlineStr"/>
@@ -2585,61 +2585,57 @@
       <c r="AD20" t="inlineStr"/>
       <c r="AE20" t="inlineStr"/>
       <c r="AF20" t="inlineStr"/>
-      <c r="AG20" t="inlineStr">
-        <is>
-          <t>Revisar: parece cafe</t>
-        </is>
-      </c>
+      <c r="AG20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>La Campiña Cocina Francesa</t>
+          <t>Sabor y Aroma</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>41</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>El Rodeo 13165, El Rodeo, Lo Barnechea, Región Metropolitana</t>
+          <t>Av. Raúl Labbé 12559, 7690554 Lo Barnechea, Región Metropolitana</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>9 4099 5970</t>
+          <t>(2) 3264 3715</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>http://lacampinafrancesa.cl/</t>
+          <t>https://saboryaroma.cl/</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Restaurante francés</t>
+          <t>Restaurante peruano</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/La+Campi%C3%B1a+Cocina+Francesa/data=!4m7!3m6!1s0x9662cb0008d7afdb:0x985d06d8abd5f9ab!8m2!3d-33.3525665!4d-70.515556!16s%2Fg%2F11yq2t7_xz!19sChIJ26_XCADLYpYRq_nVq9gGXZg?authuser=0&amp;hl=es-419&amp;rclk=1</t>
+          <t>https://www.google.com/maps/place/Sabor+y+Aroma/data=!4m7!3m6!1s0x9662cbe5e86c4a7f:0xd5d5180f7b0dcda7!8m2!3d-33.3653921!4d-70.5156354!16s%2Fg%2F11c22w2c91!19sChIJf0ps6OXLYpYRp80New8Y1dU?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-33.3525665</t>
+          <t>-33.3653921</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-70.515556</t>
+          <t>-70.5156354</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -2664,7 +2660,7 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2697,52 +2693,52 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Hansel y Gretel Restaurant y Salón de Té en el Arrayán, Lo Barnechea</t>
+          <t>Taberna Sátira Bar Restaurant</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>717</t>
+          <t>591</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Cam. los Refugios del Arrayan 15700, 7710012 Lo Barnechea, Región Metropolitana</t>
+          <t>Av. Las Condes 14878, 7710050 Lo Barnechea, Región Metropolitana</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>9 8247 6968</t>
+          <t>(2) 2215 6824</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>http://www.hanselygretel.cl/</t>
+          <t>http://www.satira.cl/</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Restaurante chileno</t>
+          <t>Bar restaurante</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Hansel+y+Gretel+Restaurant+y+Sal%C3%B3n+de+T%C3%A9+en+el+Array%C3%A1n,+Lo+Barnechea/data=!4m7!3m6!1s0x9662cb9bdd84b467:0x12df1b79a766ed94!8m2!3d-33.3607335!4d-70.4866478!16s%2Fg%2F11btxkdwrp!19sChIJZ7SE3ZvLYpYRlO1mp3kb3xI?authuser=0&amp;hl=es-419&amp;rclk=1</t>
+          <t>https://www.google.com/maps/place/Taberna+S%C3%A1tira+Bar+Restaurant/data=!4m7!3m6!1s0x9662cb910119b25b:0x21f8b1da2aee6625!8m2!3d-33.3638333!4d-70.494587!16s%2Fg%2F11bbt6n6s7!19sChIJW7IZAZHLYpYRJWbuKtqx-CE?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-33.3607335</t>
+          <t>-33.3638333</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-70.4866478</t>
+          <t>-70.494587</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -2767,7 +2763,7 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2800,52 +2796,52 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Santa Brasa Trapenses</t>
+          <t>Hansel y Gretel Restaurant y Salón de Té en el Arrayán, Lo Barnechea</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>327</t>
+          <t>718</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Av. José Alcalde Délano 10494, 7691232 Lo Barnechea, Región Metropolitana</t>
+          <t>Cam. los Refugios del Arrayan 15700, 7710012 Lo Barnechea, Región Metropolitana</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>9 5012 5729</t>
+          <t>9 8247 6968</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>http://www.santabrasa.cl/</t>
+          <t>http://www.hanselygretel.cl/</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Restaurante</t>
+          <t>Restaurante chileno</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Santa+Brasa+Trapenses/data=!4m7!3m6!1s0x9662c9f2202cde1b:0x87c84f302c81099b!8m2!3d-33.3566233!4d-70.5394682!16s%2Fg%2F11j002_66l!19sChIJG94sIPLJYpYRmwmBLDBPyIc?authuser=0&amp;hl=es-419&amp;rclk=1</t>
+          <t>https://www.google.com/maps/place/Hansel+y+Gretel+Restaurant+y+Sal%C3%B3n+de+T%C3%A9+en+el+Array%C3%A1n,+Lo+Barnechea/data=!4m7!3m6!1s0x9662cb9bdd84b467:0x12df1b79a766ed94!8m2!3d-33.3607335!4d-70.4866478!16s%2Fg%2F11btxkdwrp!19sChIJZ7SE3ZvLYpYRlO1mp3kb3xI?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-33.3566233</t>
+          <t>-33.3607335</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-70.5394682</t>
+          <t>-70.4866478</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -2870,7 +2866,7 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2903,48 +2899,52 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Arteaga</t>
+          <t>Pizzería Capri Resto Bar</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>704</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Lo Barnechea 1482, 7690228 Lo Barnechea, Región Metropolitana</t>
+          <t>El Rodeo 13052, 7690771 Lo Barnechea, Región Metropolitana</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>(2) 2216 9233</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr"/>
+          <t>9 4009 8980</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>http://www.pizzeriacapri.cl/</t>
+        </is>
+      </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Restaurante</t>
+          <t>Pizzería</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Arteaga/data=!4m7!3m6!1s0x9662cbc1992a4e89:0x90a38e190584cbb4!8m2!3d-33.355745!4d-70.5075244!16s%2Fg%2F1td59tqq!19sChIJiU4qmcHLYpYRtMuEBRmOo5A?authuser=0&amp;hl=es-419&amp;rclk=1</t>
+          <t>https://www.google.com/maps/place/Pizzer%C3%ADa+Capri+Resto+Bar/data=!4m7!3m6!1s0x9662cfdef2438a6d:0xa2cab89e9900dadb!8m2!3d-33.3522356!4d-70.5167338!16s%2Fg%2F11ngtnhh7w!19sChIJbYpD8t7PYpYR29oAmZ64yqI?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>-33.355745</t>
+          <t>-33.3522356</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>-70.5075244</t>
+          <t>-70.5167338</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -2969,12 +2969,12 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Parcial</t>
+          <t>Completo</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
@@ -3002,48 +3002,52 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>La Birra Bar (Burgers) - Mall Vivo Los Trapenses</t>
+          <t>Tio Tomate La Dehesa</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.4</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>333</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Av. José Alcalde Délano 10492, 7590932 Lo Barnechea, Región Metropolitana</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr"/>
+          <t>San Lucas 230, 7690493 Santiago, Lo Barnechea, Región Metropolitana</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>9 7661 9011</t>
+        </is>
+      </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>https://delivery.labirrabar.cl/</t>
+          <t>http://tiotomate.cl/</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hamburguesería</t>
+          <t>Restaurante</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/La+Birra+Bar+(Burgers)+-+Mall+Vivo+Los+Trapenses/@-33.356383,-70.5394653,17z/data=!3m1!4b1!4m6!3m5!1s0x9662c9006c2cb27d:0x121728200d3d01d0!8m2!3d-33.356383!4d-70.5394653!16s%2Fg%2F11x0rf5k9w?authuser=0&amp;hl=es-419&amp;entry=ttu&amp;g_ep=EgoyMDI2MDUyMC4wIKXMDSoASAFQAw%3D%3D</t>
+          <t>https://www.google.com/maps/place/Tio+Tomate+La+Dehesa/data=!4m7!3m6!1s0x9662cb099a3ff2a1:0xe32031824b1bf9be!8m2!3d-33.3628895!4d-70.512014!16s%2Fg%2F11k9s_w3ny!19sChIJofI_mgnLYpYRvvkbS4IxIOM?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>-33.356383</t>
+          <t>-33.3628895</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>-70.5394653</t>
+          <t>-70.512014</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -3068,17 +3072,17 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Sin teléfono</t>
+          <t>Completo</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="R25" t="inlineStr"/>
@@ -3096,61 +3100,53 @@
       <c r="AD25" t="inlineStr"/>
       <c r="AE25" t="inlineStr"/>
       <c r="AF25" t="inlineStr"/>
-      <c r="AG25" t="inlineStr">
-        <is>
-          <t>Revisar: parece hamburgueseria; Sin teléfono visible</t>
-        </is>
-      </c>
+      <c r="AG25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Tio Tomate La Dehesa</t>
+          <t>Ostras Chiloé - Los Trapenses</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>333</t>
+          <t>40</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>San Lucas 230, 7690493 Santiago, Lo Barnechea, Región Metropolitana</t>
+          <t>Del Monje 10548, 7700333 Lo Barnechea, Región Metropolitana</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>9 7661 9011</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>http://tiotomate.cl/</t>
-        </is>
-      </c>
+          <t>(2) 2981 6668</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Restaurante</t>
+          <t>Marisquería</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Tio+Tomate+La+Dehesa/@-33.3628895,-70.512014,17z/data=!3m1!4b1!4m6!3m5!1s0x9662cb099a3ff2a1:0xe32031824b1bf9be!8m2!3d-33.3628895!4d-70.512014!16s%2Fg%2F11k9s_w3ny?authuser=0&amp;hl=es-419&amp;entry=ttu&amp;g_ep=EgoyMDI2MDUyMC4wIKXMDSoASAFQAw%3D%3D</t>
+          <t>https://www.google.com/maps/place/Ostras+Chilo%C3%A9+-+Los+Trapenses/data=!4m7!3m6!1s0x9662c9bf05f7a90f:0x6f76b7265e34a41b!8m2!3d-33.3468895!4d-70.5423957!16s%2Fg%2F11h53xdw_d!19sChIJD6n3Bb_JYpYRG6Q0Xia3dm8?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>-33.3628895</t>
+          <t>-33.3468895</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>-70.512014</t>
+          <t>-70.5423957</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -3175,17 +3171,17 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Completo</t>
+          <t>Parcial</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="R26" t="inlineStr"/>
@@ -3208,48 +3204,52 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Hostería Las Delicias</t>
+          <t>Brunapoli Los Trapenses</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>176</t>
+          <t>74</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Av. Raúl Labbé 14998, Lo Barnechea, Región Metropolitana</t>
+          <t>Mall Vivo Los Trapenses, Av. José Alcalde Délano 10545, Local 1062, Lo Barnechea, Región Metropolitana</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>(2) 2321 5986</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr"/>
+          <t>9 3940 5997</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>http://www.brunapoli.cl/</t>
+        </is>
+      </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Restaurante</t>
+          <t>Restaurante italiano</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Hoster%C3%ADa+Las+Delicias/data=!4m7!3m6!1s0x9662cb90dc3a27ef:0x26faa166521d873d!8m2!3d-33.3621111!4d-70.4935024!16s%2Fg%2F1th0zkk6!19sChIJ7yc63JDLYpYRPYcdUmah-iY?authuser=0&amp;hl=es-419&amp;rclk=1</t>
+          <t>https://www.google.com/maps/place/Brunapoli+Los+Trapenses/data=!4m7!3m6!1s0x9662c96f48addef7:0xb67cff29f4616058!8m2!3d-33.3564637!4d-70.5394709!16s%2Fg%2F11f055lzxt!19sChIJ996tSG_JYpYRWGBh9Cn_fLY?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>-33.3621111</t>
+          <t>-33.3564637</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>-70.4935024</t>
+          <t>-70.5394709</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Parcial</t>
+          <t>Completo</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
@@ -3307,52 +3307,52 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>China 365 lo Barnechea</t>
+          <t>BRU Italian Bakery</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>373</t>
+          <t>56</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>El Rodeo 13318, 7690000 Lo Barnechea, Región Metropolitana</t>
+          <t>Mall Vivo Los Trapenses, Av. José Alcalde Délano 10533, Local 1004, 7691231 Lo Barnechea, Región Metropolitana</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>9 8888 8365</t>
+          <t>(2) 2993 2116</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>http://www.china365.cl/</t>
+          <t>http://www.brubakery.cl/</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Restaurante chino</t>
+          <t>Restaurante italiano</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/China+365+lo+Barnechea/data=!4m7!3m6!1s0x9662cbaebd15089b:0xba450f6d15f7927a!8m2!3d-33.3517486!4d-70.5132361!16s%2Fg%2F11gzs5s45z!19sChIJmwgVva7LYpYRepL3FW0PRbo?authuser=0&amp;hl=es-419&amp;rclk=1</t>
+          <t>https://www.google.com/maps/place/BRU+Italian+Bakery/data=!4m7!3m6!1s0x9662c90870d02f6f:0x49622a992a37a51d!8m2!3d-33.3571631!4d-70.5405466!16s%2Fg%2F11rmp5p_pb!19sChIJby_QcAjJYpYRHaU3KpkqYkk?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>-33.3517486</t>
+          <t>-33.3571631</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>-70.5132361</t>
+          <t>-70.5405466</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3407,8 +3407,309 @@
       <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="inlineStr"/>
     </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>alBosque - CraftBeers &amp; Food</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>299</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Cam. Los Trapenses 3200, 7700334 Lo Barnechea, Región Metropolitana</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>https://fiweex.com/reservas_portal_bienvenida/aYF6hA%3D%3D?fbclid=PAQ0xDSwLac_hleHRuA2FlbQIxMQABp_QkBhlpK2_HIjbcz4csm2C7ocjJpYWLib1A2-NH1VYU063iyZ4QjRxoGxq1_aem_QZNMjppiOC69cYSkU9JLYw</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Restaurante</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/alBosque+-+CraftBeers+%26+Food/data=!4m7!3m6!1s0x9662c95390865deb:0x1a0bf66d75eb5554!8m2!3d-33.346813!4d-70.5433961!16s%2Fg%2F11r_v5k08f!19sChIJ612GkFPJYpYRVFXrdW32Cxo?authuser=0&amp;hl=es-419&amp;rclk=1</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>-33.346813</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>-70.5433961</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Lo Barnechea</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Google Maps web scraping con Playwright</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Sin teléfono</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr"/>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="inlineStr"/>
+      <c r="W29" t="inlineStr"/>
+      <c r="X29" t="inlineStr"/>
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="inlineStr"/>
+      <c r="AA29" t="inlineStr"/>
+      <c r="AB29" t="inlineStr"/>
+      <c r="AC29" t="inlineStr"/>
+      <c r="AD29" t="inlineStr"/>
+      <c r="AE29" t="inlineStr"/>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="inlineStr">
+        <is>
+          <t>Sin teléfono visible</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Restaurant Valle Escondido</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Lo Barnechea, Región Metropolitana</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Restaurante</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Restaurant+Valle+Escondido/data=!4m7!3m6!1s0x9662cba34e975a89:0xd84fddbbfc111471!8m2!3d-33.3506037!4d-70.4903391!16s%2Fg%2F11d_31qrdn!19sChIJiVqXTqPLYpYRcRQR_LvdT9g?authuser=0&amp;hl=es-419&amp;rclk=1</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>-33.3506037</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>-70.4903391</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Lo Barnechea</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>Google Maps web scraping con Playwright</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Sin teléfono</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="inlineStr"/>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr"/>
+      <c r="V30" t="inlineStr"/>
+      <c r="W30" t="inlineStr"/>
+      <c r="X30" t="inlineStr"/>
+      <c r="Y30" t="inlineStr"/>
+      <c r="Z30" t="inlineStr"/>
+      <c r="AA30" t="inlineStr"/>
+      <c r="AB30" t="inlineStr"/>
+      <c r="AC30" t="inlineStr"/>
+      <c r="AD30" t="inlineStr"/>
+      <c r="AE30" t="inlineStr"/>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="inlineStr">
+        <is>
+          <t>Sin teléfono visible</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Hostería Las Delicias</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Av. Raúl Labbé 14998, Lo Barnechea, Región Metropolitana</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>(2) 2321 5986</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Restaurante</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Hoster%C3%ADa+Las+Delicias/data=!4m7!3m6!1s0x9662cb90dc3a27ef:0x26faa166521d873d!8m2!3d-33.3621111!4d-70.4935024!16s%2Fg%2F1th0zkk6!19sChIJ7yc63JDLYpYRPYcdUmah-iY?authuser=0&amp;hl=es-419&amp;rclk=1</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>-33.3621111</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>-70.4935024</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Lo Barnechea</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Google Maps web scraping con Playwright</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr"/>
+      <c r="S31" t="inlineStr"/>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr"/>
+      <c r="V31" t="inlineStr"/>
+      <c r="W31" t="inlineStr"/>
+      <c r="X31" t="inlineStr"/>
+      <c r="Y31" t="inlineStr"/>
+      <c r="Z31" t="inlineStr"/>
+      <c r="AA31" t="inlineStr"/>
+      <c r="AB31" t="inlineStr"/>
+      <c r="AC31" t="inlineStr"/>
+      <c r="AD31" t="inlineStr"/>
+      <c r="AE31" t="inlineStr"/>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AG28"/>
+  <autoFilter ref="A1:AG31"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>